--- a/artfynd/A 39065-2023 artfynd.xlsx
+++ b/artfynd/A 39065-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39065-2023 artfynd.xlsx
+++ b/artfynd/A 39065-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,6 +1098,394 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125807661</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>492500</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6939872</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125807662</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>492488</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6939874</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125807665</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80030</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>492424</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6939865</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125807664</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>492468</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6939853</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erik Wilhelmsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39065-2023 artfynd.xlsx
+++ b/artfynd/A 39065-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1486,6 +1486,740 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125777612</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>492406</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6939892</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>125777679</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91795</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>760</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön , Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>492420</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6939877</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125777756</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98328</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön , Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>492433</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6939865</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125777687</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön , Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>492420</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6939877</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125777790</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98328</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön , Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>492448</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6939847</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125777697</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98328</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön , Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>492420</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6939877</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125777647</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80105</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Rogstabodsjön , Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>492397</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6939893</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39065-2023 artfynd.xlsx
+++ b/artfynd/A 39065-2023 artfynd.xlsx
@@ -1200,7 +1200,7 @@
         <v>125807662</v>
       </c>
       <c r="B7" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>125807664</v>
       </c>
       <c r="B9" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>125777679</v>
       </c>
       <c r="B11" t="n">
-        <v>91795</v>
+        <v>91798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>125777756</v>
       </c>
       <c r="B12" t="n">
-        <v>98328</v>
+        <v>98331</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>125777790</v>
       </c>
       <c r="B14" t="n">
-        <v>98328</v>
+        <v>98331</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>125777697</v>
       </c>
       <c r="B15" t="n">
-        <v>98328</v>
+        <v>98331</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 39065-2023 artfynd.xlsx
+++ b/artfynd/A 39065-2023 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>125807661</v>
       </c>
       <c r="B6" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>125807662</v>
       </c>
       <c r="B7" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>125807665</v>
       </c>
       <c r="B8" t="n">
-        <v>80030</v>
+        <v>80031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>125807664</v>
       </c>
       <c r="B9" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125777612</v>
+        <v>125777679</v>
       </c>
       <c r="B10" t="n">
-        <v>80070</v>
+        <v>91799</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1522,14 +1522,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rogstabodsjön, Jmt</t>
+          <t>Rogstabodsjön , Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492406</v>
+        <v>492420</v>
       </c>
       <c r="R10" t="n">
-        <v>6939892</v>
+        <v>6939877</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125777679</v>
+        <v>125777612</v>
       </c>
       <c r="B11" t="n">
-        <v>91798</v>
+        <v>80071</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1623,14 +1623,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rogstabodsjön , Jmt</t>
+          <t>Rogstabodsjön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492420</v>
+        <v>492406</v>
       </c>
       <c r="R11" t="n">
-        <v>6939877</v>
+        <v>6939892</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
         <v>125777756</v>
       </c>
       <c r="B12" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>125777687</v>
       </c>
       <c r="B13" t="n">
-        <v>80071</v>
+        <v>80072</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>125777790</v>
       </c>
       <c r="B14" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>125777697</v>
       </c>
       <c r="B15" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>125777647</v>
       </c>
       <c r="B16" t="n">
-        <v>80105</v>
+        <v>80106</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 39065-2023 artfynd.xlsx
+++ b/artfynd/A 39065-2023 artfynd.xlsx
@@ -1200,7 +1200,7 @@
         <v>125807662</v>
       </c>
       <c r="B7" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>125807664</v>
       </c>
       <c r="B9" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>125777679</v>
       </c>
       <c r="B10" t="n">
-        <v>91799</v>
+        <v>91802</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>125777756</v>
       </c>
       <c r="B12" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>125777790</v>
       </c>
       <c r="B14" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>125777697</v>
       </c>
       <c r="B15" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 39065-2023 artfynd.xlsx
+++ b/artfynd/A 39065-2023 artfynd.xlsx
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125777679</v>
+        <v>125777612</v>
       </c>
       <c r="B10" t="n">
-        <v>91802</v>
+        <v>80071</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1522,14 +1522,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rogstabodsjön , Jmt</t>
+          <t>Rogstabodsjön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492420</v>
+        <v>492406</v>
       </c>
       <c r="R10" t="n">
-        <v>6939877</v>
+        <v>6939892</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125777612</v>
+        <v>125777679</v>
       </c>
       <c r="B11" t="n">
-        <v>80071</v>
+        <v>91802</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1623,14 +1623,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rogstabodsjön, Jmt</t>
+          <t>Rogstabodsjön , Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492406</v>
+        <v>492420</v>
       </c>
       <c r="R11" t="n">
-        <v>6939892</v>
+        <v>6939877</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 39065-2023 artfynd.xlsx
+++ b/artfynd/A 39065-2023 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>125807661</v>
       </c>
       <c r="B6" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>125807662</v>
       </c>
       <c r="B7" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>125807665</v>
       </c>
       <c r="B8" t="n">
-        <v>80031</v>
+        <v>80035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>125807664</v>
       </c>
       <c r="B9" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125777612</v>
+        <v>125777679</v>
       </c>
       <c r="B10" t="n">
-        <v>80071</v>
+        <v>91806</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1522,14 +1522,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rogstabodsjön, Jmt</t>
+          <t>Rogstabodsjön , Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492406</v>
+        <v>492420</v>
       </c>
       <c r="R10" t="n">
-        <v>6939892</v>
+        <v>6939877</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125777679</v>
+        <v>125777612</v>
       </c>
       <c r="B11" t="n">
-        <v>91802</v>
+        <v>80075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1623,14 +1623,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rogstabodsjön , Jmt</t>
+          <t>Rogstabodsjön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492420</v>
+        <v>492406</v>
       </c>
       <c r="R11" t="n">
-        <v>6939877</v>
+        <v>6939892</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
         <v>125777756</v>
       </c>
       <c r="B12" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>125777687</v>
       </c>
       <c r="B13" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>125777790</v>
       </c>
       <c r="B14" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>125777697</v>
       </c>
       <c r="B15" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>125777647</v>
       </c>
       <c r="B16" t="n">
-        <v>80106</v>
+        <v>80110</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 39065-2023 artfynd.xlsx
+++ b/artfynd/A 39065-2023 artfynd.xlsx
@@ -1200,7 +1200,7 @@
         <v>125807662</v>
       </c>
       <c r="B7" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>125807664</v>
       </c>
       <c r="B9" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125777679</v>
+        <v>125777612</v>
       </c>
       <c r="B10" t="n">
-        <v>91806</v>
+        <v>80075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1522,14 +1522,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rogstabodsjön , Jmt</t>
+          <t>Rogstabodsjön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492420</v>
+        <v>492406</v>
       </c>
       <c r="R10" t="n">
-        <v>6939877</v>
+        <v>6939892</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125777612</v>
+        <v>125777679</v>
       </c>
       <c r="B11" t="n">
-        <v>80075</v>
+        <v>91806</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1623,14 +1623,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rogstabodsjön, Jmt</t>
+          <t>Rogstabodsjön , Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492406</v>
+        <v>492420</v>
       </c>
       <c r="R11" t="n">
-        <v>6939892</v>
+        <v>6939877</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
         <v>125777756</v>
       </c>
       <c r="B12" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>125777790</v>
       </c>
       <c r="B14" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>125777697</v>
       </c>
       <c r="B15" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 39065-2023 artfynd.xlsx
+++ b/artfynd/A 39065-2023 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>125807661</v>
       </c>
       <c r="B6" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>125807662</v>
       </c>
       <c r="B7" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>125807665</v>
       </c>
       <c r="B8" t="n">
-        <v>80035</v>
+        <v>80036</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>125807664</v>
       </c>
       <c r="B9" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125777612</v>
+        <v>125777679</v>
       </c>
       <c r="B10" t="n">
-        <v>80075</v>
+        <v>91808</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1522,14 +1522,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rogstabodsjön, Jmt</t>
+          <t>Rogstabodsjön , Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492406</v>
+        <v>492420</v>
       </c>
       <c r="R10" t="n">
-        <v>6939892</v>
+        <v>6939877</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125777679</v>
+        <v>125777612</v>
       </c>
       <c r="B11" t="n">
-        <v>91806</v>
+        <v>80076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1623,14 +1623,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rogstabodsjön , Jmt</t>
+          <t>Rogstabodsjön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492420</v>
+        <v>492406</v>
       </c>
       <c r="R11" t="n">
-        <v>6939877</v>
+        <v>6939892</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
         <v>125777756</v>
       </c>
       <c r="B12" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>125777687</v>
       </c>
       <c r="B13" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>125777790</v>
       </c>
       <c r="B14" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>125777697</v>
       </c>
       <c r="B15" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>125777647</v>
       </c>
       <c r="B16" t="n">
-        <v>80110</v>
+        <v>80111</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 39065-2023 artfynd.xlsx
+++ b/artfynd/A 39065-2023 artfynd.xlsx
@@ -1200,7 +1200,7 @@
         <v>125807662</v>
       </c>
       <c r="B7" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>125807664</v>
       </c>
       <c r="B9" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>125777679</v>
       </c>
       <c r="B10" t="n">
-        <v>91808</v>
+        <v>91810</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>125777756</v>
       </c>
       <c r="B12" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>125777790</v>
       </c>
       <c r="B14" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>125777697</v>
       </c>
       <c r="B15" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 39065-2023 artfynd.xlsx
+++ b/artfynd/A 39065-2023 artfynd.xlsx
@@ -1200,7 +1200,7 @@
         <v>125807662</v>
       </c>
       <c r="B7" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>125807664</v>
       </c>
       <c r="B9" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>125777679</v>
       </c>
       <c r="B10" t="n">
-        <v>91810</v>
+        <v>91812</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>125777756</v>
       </c>
       <c r="B12" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>125777790</v>
       </c>
       <c r="B14" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>125777697</v>
       </c>
       <c r="B15" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 39065-2023 artfynd.xlsx
+++ b/artfynd/A 39065-2023 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>125807661</v>
       </c>
       <c r="B6" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>125807662</v>
       </c>
       <c r="B7" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>125807665</v>
       </c>
       <c r="B8" t="n">
-        <v>80036</v>
+        <v>80040</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>125807664</v>
       </c>
       <c r="B9" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125777679</v>
+        <v>125777612</v>
       </c>
       <c r="B10" t="n">
-        <v>91812</v>
+        <v>80080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1522,14 +1522,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rogstabodsjön , Jmt</t>
+          <t>Rogstabodsjön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492420</v>
+        <v>492406</v>
       </c>
       <c r="R10" t="n">
-        <v>6939877</v>
+        <v>6939892</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125777612</v>
+        <v>125777679</v>
       </c>
       <c r="B11" t="n">
-        <v>80076</v>
+        <v>91816</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1623,14 +1623,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rogstabodsjön, Jmt</t>
+          <t>Rogstabodsjön , Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492406</v>
+        <v>492420</v>
       </c>
       <c r="R11" t="n">
-        <v>6939892</v>
+        <v>6939877</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
         <v>125777756</v>
       </c>
       <c r="B12" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>125777687</v>
       </c>
       <c r="B13" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>125777790</v>
       </c>
       <c r="B14" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>125777697</v>
       </c>
       <c r="B15" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>125777647</v>
       </c>
       <c r="B16" t="n">
-        <v>80111</v>
+        <v>80115</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 39065-2023 artfynd.xlsx
+++ b/artfynd/A 39065-2023 artfynd.xlsx
@@ -1200,7 +1200,7 @@
         <v>125807662</v>
       </c>
       <c r="B7" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>125807664</v>
       </c>
       <c r="B9" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125777612</v>
+        <v>125777679</v>
       </c>
       <c r="B10" t="n">
-        <v>80080</v>
+        <v>91816</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1522,14 +1522,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rogstabodsjön, Jmt</t>
+          <t>Rogstabodsjön , Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492406</v>
+        <v>492420</v>
       </c>
       <c r="R10" t="n">
-        <v>6939892</v>
+        <v>6939877</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125777679</v>
+        <v>125777612</v>
       </c>
       <c r="B11" t="n">
-        <v>91816</v>
+        <v>80080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1623,14 +1623,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rogstabodsjön , Jmt</t>
+          <t>Rogstabodsjön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492420</v>
+        <v>492406</v>
       </c>
       <c r="R11" t="n">
-        <v>6939877</v>
+        <v>6939892</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1693,7 @@
         <v>125777756</v>
       </c>
       <c r="B12" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>125777790</v>
       </c>
       <c r="B14" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>125777697</v>
       </c>
       <c r="B15" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 39065-2023 artfynd.xlsx
+++ b/artfynd/A 39065-2023 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>125807661</v>
       </c>
       <c r="B6" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>125807662</v>
       </c>
       <c r="B7" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>125807665</v>
       </c>
       <c r="B8" t="n">
-        <v>80040</v>
+        <v>80043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>125807664</v>
       </c>
       <c r="B9" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>125777679</v>
       </c>
       <c r="B10" t="n">
-        <v>91816</v>
+        <v>91819</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>125777612</v>
       </c>
       <c r="B11" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>125777756</v>
       </c>
       <c r="B12" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>125777687</v>
       </c>
       <c r="B13" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>125777790</v>
       </c>
       <c r="B14" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>125777697</v>
       </c>
       <c r="B15" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         <v>125777647</v>
       </c>
       <c r="B16" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 39065-2023 artfynd.xlsx
+++ b/artfynd/A 39065-2023 artfynd.xlsx
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125777679</v>
+        <v>125777612</v>
       </c>
       <c r="B10" t="n">
-        <v>91819</v>
+        <v>80083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1522,14 +1522,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rogstabodsjön , Jmt</t>
+          <t>Rogstabodsjön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492420</v>
+        <v>492406</v>
       </c>
       <c r="R10" t="n">
-        <v>6939877</v>
+        <v>6939892</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125777612</v>
+        <v>125777679</v>
       </c>
       <c r="B11" t="n">
-        <v>80083</v>
+        <v>91819</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1623,14 +1623,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rogstabodsjön, Jmt</t>
+          <t>Rogstabodsjön , Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492406</v>
+        <v>492420</v>
       </c>
       <c r="R11" t="n">
-        <v>6939892</v>
+        <v>6939877</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 39065-2023 artfynd.xlsx
+++ b/artfynd/A 39065-2023 artfynd.xlsx
@@ -1488,32 +1488,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125777612</v>
+        <v>125777679</v>
       </c>
       <c r="B10" t="n">
-        <v>80083</v>
+        <v>91819</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1522,14 +1522,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rogstabodsjön, Jmt</t>
+          <t>Rogstabodsjön , Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492406</v>
+        <v>492420</v>
       </c>
       <c r="R10" t="n">
-        <v>6939892</v>
+        <v>6939877</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1589,32 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125777679</v>
+        <v>125777612</v>
       </c>
       <c r="B11" t="n">
-        <v>91819</v>
+        <v>80083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1623,14 +1623,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rogstabodsjön , Jmt</t>
+          <t>Rogstabodsjön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492420</v>
+        <v>492406</v>
       </c>
       <c r="R11" t="n">
-        <v>6939877</v>
+        <v>6939892</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 39065-2023 artfynd.xlsx
+++ b/artfynd/A 39065-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125777552</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125777679</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111624591</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111624117</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111624220</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125777687</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1375,6 +1410,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807659</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115643503</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115643582</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1678,6 +1728,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125777545</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125777612</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1876,6 +1936,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807661</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1977,6 +2042,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125777539</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2078,6 +2148,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125777647</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2180,6 +2255,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111624105</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2290,6 +2370,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125777591</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2400,6 +2485,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125777697</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2510,6 +2600,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125777756</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2620,6 +2715,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125777790</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2722,6 +2822,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125779022</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2819,6 +2924,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807662</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2916,6 +3026,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807664</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3017,6 +3132,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125777523</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3114,8 +3234,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125807665</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>